--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="1245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="1246">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -3747,6 +3747,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.0403999984264374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0469999983906746</t>
   </si>
 </sst>
 </file>
@@ -68721,7 +68724,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6513888889</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>6749715</v>
@@ -68742,6 +68745,32 @@
         <v>1101</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6504166667</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>4047803</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>0.0540000014007092</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>0.0472000017762184</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>0.0513999983668327</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>0.0469999983906746</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -68750,7 +68750,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6504166667</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>4047803</v>
@@ -68759,7 +68759,7 @@
         <v>0.0540000014007092</v>
       </c>
       <c r="D2488" t="n">
-        <v>0.0472000017762184</v>
+        <v>0.0469999983906746</v>
       </c>
       <c r="E2488" t="n">
         <v>0.0513999983668327</v>
@@ -68771,6 +68771,32 @@
         <v>1245</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6493171296</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>1418140</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>0.0498000010848045</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>0.0419999994337559</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>0.0498000010848045</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>0.0423999987542629</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1234</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -68776,7 +68776,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6493171296</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>1418140</v>
@@ -68797,6 +68797,32 @@
         <v>1234</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6496180556</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>1239702</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>0.0458000004291534</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>0.0458000004291534</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>0.0414000004529953</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1236</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="1246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="1247">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -3750,6 +3750,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.0469999983906746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0417999997735023</t>
   </si>
 </sst>
 </file>
@@ -68802,7 +68805,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6496180556</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>1239702</v>
@@ -68823,6 +68826,32 @@
         <v>1236</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6495138889</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>382357</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>0.0421999990940094</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>0.0421999990940094</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>0.0417999997735023</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1246</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -68831,7 +68831,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6495138889</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>382357</v>
@@ -68852,6 +68852,32 @@
         <v>1246</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6495486111</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>267915</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>0.0417999997735023</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>0.0395999997854233</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>0.0416000001132488</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>0.0419999994337559</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -68857,13 +68857,13 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6495486111</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>267915</v>
       </c>
       <c r="C2492" t="n">
-        <v>0.0417999997735023</v>
+        <v>0.0419999994337559</v>
       </c>
       <c r="D2492" t="n">
         <v>0.0395999997854233</v>
@@ -68878,6 +68878,32 @@
         <v>1120</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.649849537</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>3461627</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>0.049600001424551</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>0.0421999990940094</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>0.046000000089407</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>0.044599998742342</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1232</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -68883,7 +68883,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.649849537</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>3461627</v>
@@ -68904,6 +68904,32 @@
         <v>1232</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6505324074</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>952776</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>0.0465999990701675</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>0.0414000004529953</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>0.0465999990701675</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>0.0419999994337559</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="1247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="1248">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -3753,6 +3753,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.0417999997735023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0406000018119812</t>
   </si>
 </sst>
 </file>
@@ -68909,7 +68912,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6505324074</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>952776</v>
@@ -68930,6 +68933,32 @@
         <v>1120</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6493287037</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>609764</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>0.0414000004529953</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>0.0392000004649162</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>0.0414000004529953</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>0.0406000018119812</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1247</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="1248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="1249">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -3756,6 +3756,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.0406000018119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0401999987661839</t>
   </si>
 </sst>
 </file>
@@ -68938,7 +68941,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6493287037</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>609764</v>
@@ -68959,6 +68962,32 @@
         <v>1247</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6494097222</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>139688</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>0.0419999994337559</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>0.0401999987661839</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1248</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -68967,7 +68967,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6494097222</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>139688</v>
@@ -68988,6 +68988,32 @@
         <v>1248</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.633287037</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>227424</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>0.0419999994337559</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>0.0395999997854233</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>0.0416000001132488</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>0.0410000011324883</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -68993,7 +68993,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.633287037</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>227424</v>
@@ -69014,6 +69014,32 @@
         <v>1121</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6642592593</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>227641</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>0.0416000001132488</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>0.0395999997854233</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>0.0416000001132488</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>0.0408000014722347</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69019,7 +69019,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6642592593</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>227641</v>
@@ -69040,6 +69040,32 @@
         <v>1243</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6331365741</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>223905</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>0.0412000007927418</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>0.0408000014722347</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69045,7 +69045,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6331365741</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>223905</v>
@@ -69066,6 +69066,32 @@
         <v>1243</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6911111111</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>485573</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>0.0410000011324883</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>0.0403999984264374</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1244</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69071,7 +69071,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6911111111</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>485573</v>
@@ -69092,6 +69092,32 @@
         <v>1244</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.654837963</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>124000</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>0.0403999984264374</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>0.0392000004649162</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>0.0403999984264374</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69097,7 +69097,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.654837963</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>124000</v>
@@ -69118,6 +69118,32 @@
         <v>1207</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6270138889</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>69183</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>0.0395999997854233</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1190</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69123,7 +69123,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6270138889</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>69183</v>
@@ -69144,6 +69144,32 @@
         <v>1190</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6912268518</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>331223</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>0.0392000004649162</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69149,7 +69149,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6912268518</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>331223</v>
@@ -69170,6 +69170,32 @@
         <v>1207</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6686689815</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>395269</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>0.0430000014603138</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>0.0430000014603138</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1122</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69175,7 +69175,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6686689815</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>395269</v>
@@ -69196,6 +69196,32 @@
         <v>1122</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6910532407</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>330158</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>0.0443999990820885</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>0.0406000018119812</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>0.0430000014603138</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>0.0419999994337559</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69201,25 +69201,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6910532407</v>
+        <v>45967.691087963</v>
       </c>
       <c r="B2505" t="n">
-        <v>330158</v>
+        <v>362823</v>
       </c>
       <c r="C2505" t="n">
-        <v>0.0443999990820885</v>
+        <v>0.0439999997615814</v>
       </c>
       <c r="D2505" t="n">
-        <v>0.0406000018119812</v>
+        <v>0.0395999997854233</v>
       </c>
       <c r="E2505" t="n">
-        <v>0.0430000014603138</v>
+        <v>0.0439999997615814</v>
       </c>
       <c r="F2505" t="n">
-        <v>0.0419999994337559</v>
+        <v>0.0410000011324883</v>
       </c>
       <c r="G2505" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69201,25 +69201,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.691087963</v>
+        <v>45968.6912615741</v>
       </c>
       <c r="B2505" t="n">
-        <v>362823</v>
+        <v>138371</v>
       </c>
       <c r="C2505" t="n">
-        <v>0.0439999997615814</v>
+        <v>0.0417999997735023</v>
       </c>
       <c r="D2505" t="n">
         <v>0.0395999997854233</v>
       </c>
       <c r="E2505" t="n">
-        <v>0.0439999997615814</v>
+        <v>0.0410000011324883</v>
       </c>
       <c r="F2505" t="n">
-        <v>0.0410000011324883</v>
+        <v>0.0417999997735023</v>
       </c>
       <c r="G2505" t="s">
-        <v>1121</v>
+        <v>1246</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69201,27 +69201,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6912615741</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
+        <v>330158</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>0.0443999990820885</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>0.0406000018119812</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>0.0430000014603138</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>0.0419999994337559</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>362823</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>0.0439999997615814</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>0.0395999997854233</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>0.0439999997615814</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>0.0410000011324883</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
         <v>138371</v>
       </c>
-      <c r="C2505" t="n">
+      <c r="C2507" t="n">
         <v>0.0417999997735023</v>
       </c>
-      <c r="D2505" t="n">
+      <c r="D2507" t="n">
         <v>0.0395999997854233</v>
       </c>
-      <c r="E2505" t="n">
+      <c r="E2507" t="n">
         <v>0.0410000011324883</v>
       </c>
-      <c r="F2505" t="n">
+      <c r="F2507" t="n">
         <v>0.0417999997735023</v>
       </c>
-      <c r="G2505" t="s">
+      <c r="G2507" t="s">
         <v>1246</v>
       </c>
-      <c r="H2505" t="s">
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6197569444</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>0.0438000001013279</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>0.0438000001013279</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>0.0428000018000603</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69279,7 +69279,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6197569444</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>20000</v>
@@ -69300,6 +69300,32 @@
         <v>1228</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6912037037</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>166599</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>0.0417999997735023</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>0.0395999997854233</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69305,7 +69305,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6912037037</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>166599</v>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69329,6 +69329,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.3333333333</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69355,6 +69355,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.3333333333</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.6910648148</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>35907</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>0.0419999994337559</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>0.0395999997854233</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>0.0419999994337559</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>0.0395999997854233</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>1190</v>
+      </c>
+      <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69383,7 +69383,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6910648148</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>35907</v>
@@ -69404,6 +69404,32 @@
         <v>1190</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6491435185</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>4203</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69409,7 +69409,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6491435185</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>4203</v>
@@ -69430,6 +69430,32 @@
         <v>1224</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6273032407</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>418380</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>0.0392000004649162</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>0.0392000004649162</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>0.0381999984383583</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1241</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69435,7 +69435,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6273032407</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>418380</v>
@@ -69456,6 +69456,32 @@
         <v>1241</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6494097222</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>110500</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>0.0381999984383583</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69461,7 +69461,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6494097222</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>110500</v>
@@ -69482,6 +69482,32 @@
         <v>1211</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6671412037</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>256000</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69487,7 +69487,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6671412037</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>256000</v>
@@ -69508,6 +69508,32 @@
         <v>1211</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6641666667</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>284765</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>0.0359999984502792</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>0.0377999991178513</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>0.0359999984502792</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69513,7 +69513,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6641666667</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>284765</v>
@@ -69534,6 +69534,32 @@
         <v>1124</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6469097222</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>104538</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>0.0388000011444092</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>0.0370000004768372</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>0.0372000001370907</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>0.0388000011444092</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>1239</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69539,7 +69539,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6469097222</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>104538</v>
@@ -69560,6 +69560,32 @@
         <v>1239</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6910069444</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>11659</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>0.0384000018239021</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>0.0384000018239021</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>1212</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69565,7 +69565,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6910069444</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>11659</v>
@@ -69586,6 +69586,32 @@
         <v>1212</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6169675926</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>143790</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>0.0388000011444092</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69591,7 +69591,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6169675926</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>143790</v>
@@ -69612,6 +69612,32 @@
         <v>1123</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6762037037</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>0.0373999997973442</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>0.0392000004649162</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69617,7 +69617,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.6762037037</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>150000</v>
@@ -69638,6 +69638,32 @@
         <v>1238</v>
       </c>
       <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.6910763889</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>205014</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>0.0392000004649162</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>0.0373999997973442</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>0.0373999997973442</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>0.0377999991178513</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>1242</v>
+      </c>
+      <c r="H2522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69643,7 +69643,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.6910763889</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>205014</v>
@@ -69664,6 +69664,32 @@
         <v>1242</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.4115625</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>43200</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>0.0377999991178513</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>0.0392000004649162</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>0.0377999991178513</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>1242</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69669,7 +69669,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>45992.4115625</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2523" t="n">
         <v>43200</v>
@@ -69690,6 +69690,32 @@
         <v>1242</v>
       </c>
       <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.4726851852</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>2700</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H2524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69695,7 +69695,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.4726851852</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>2700</v>
@@ -69716,6 +69716,32 @@
         <v>1237</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.691099537</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>71005</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>0.0375999994575977</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>0.0373999997973442</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69721,7 +69721,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.691099537</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>71005</v>
@@ -69730,7 +69730,7 @@
         <v>0.0394000001251698</v>
       </c>
       <c r="D2525" t="n">
-        <v>0.0375999994575977</v>
+        <v>0.0373999997973442</v>
       </c>
       <c r="E2525" t="n">
         <v>0.0394000001251698</v>
@@ -69742,6 +69742,32 @@
         <v>1221</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6551157407</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>442976</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>0.0388000011444092</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>0.0373999997973442</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>0.0373999997973442</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>0.0373999997973442</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69747,7 +69747,7 @@
     </row>
     <row r="2526">
       <c r="A2526" s="1" t="n">
-        <v>45995.6551157407</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B2526" t="n">
         <v>442976</v>
@@ -69768,6 +69768,32 @@
         <v>1221</v>
       </c>
       <c r="H2526" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" s="1" t="n">
+        <v>45996.5751388889</v>
+      </c>
+      <c r="B2527" t="n">
+        <v>57694</v>
+      </c>
+      <c r="C2527" t="n">
+        <v>0.0373999997973442</v>
+      </c>
+      <c r="D2527" t="n">
+        <v>0.0373999997973442</v>
+      </c>
+      <c r="E2527" t="n">
+        <v>0.0373999997973442</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>0.0373999997973442</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H2527" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69773,7 +69773,7 @@
     </row>
     <row r="2527">
       <c r="A2527" s="1" t="n">
-        <v>45996.5751388889</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2527" t="n">
         <v>57694</v>
@@ -69794,6 +69794,32 @@
         <v>1221</v>
       </c>
       <c r="H2527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>45999.6911921296</v>
+      </c>
+      <c r="B2528" t="n">
+        <v>1299409</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>0.0392000004649162</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H2528" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69799,7 +69799,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.6911921296</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>1299409</v>
@@ -69820,6 +69820,32 @@
         <v>1123</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.6934027778</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>3220971</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>0.0489999987185001</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>0.0366000011563301</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>0.0489999987185001</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69825,7 +69825,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6934027778</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>3220971</v>
@@ -69846,6 +69846,32 @@
         <v>1202</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.6928125</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>2143427</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>0.0527999997138977</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>0.0410000011324883</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>0.0507999993860722</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>0.0419999994337559</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69851,7 +69851,7 @@
     </row>
     <row r="2530">
       <c r="A2530" s="1" t="n">
-        <v>46001.6928125</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2530" t="n">
         <v>2143427</v>
@@ -69872,6 +69872,32 @@
         <v>1120</v>
       </c>
       <c r="H2530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" s="1" t="n">
+        <v>46002.6912847222</v>
+      </c>
+      <c r="B2531" t="n">
+        <v>899937</v>
+      </c>
+      <c r="C2531" t="n">
+        <v>0.0430000014603138</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>0.0430000014603138</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>0.0408000014722347</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H2531" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69877,7 +69877,7 @@
     </row>
     <row r="2531">
       <c r="A2531" s="1" t="n">
-        <v>46002.6912847222</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2531" t="n">
         <v>899937</v>
@@ -69898,6 +69898,32 @@
         <v>1243</v>
       </c>
       <c r="H2531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46003.6916550926</v>
+      </c>
+      <c r="B2532" t="n">
+        <v>423887</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>0.0438000001013279</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>0.0417999997735023</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H2532" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69903,7 +69903,7 @@
     </row>
     <row r="2532">
       <c r="A2532" s="1" t="n">
-        <v>46003.6916550926</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2532" t="n">
         <v>423887</v>
@@ -69924,6 +69924,32 @@
         <v>1207</v>
       </c>
       <c r="H2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46006.6911111111</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>485699</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>0.0423999987542629</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>0.0388000011444092</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>0.0395999997854233</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H2533" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69929,7 +69929,7 @@
     </row>
     <row r="2533">
       <c r="A2533" s="1" t="n">
-        <v>46006.6911111111</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2533" t="n">
         <v>485699</v>
@@ -69950,6 +69950,32 @@
         <v>1237</v>
       </c>
       <c r="H2533" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46007.69125</v>
+      </c>
+      <c r="B2534" t="n">
+        <v>55292</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H2534" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69955,7 +69955,7 @@
     </row>
     <row r="2534">
       <c r="A2534" s="1" t="n">
-        <v>46007.69125</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2534" t="n">
         <v>55292</v>
@@ -69976,6 +69976,32 @@
         <v>1123</v>
       </c>
       <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.4878703704</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>292245</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H2535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -69981,7 +69981,7 @@
     </row>
     <row r="2535">
       <c r="A2535" s="1" t="n">
-        <v>46008.4878703704</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B2535" t="n">
         <v>292245</v>
@@ -70002,6 +70002,32 @@
         <v>1224</v>
       </c>
       <c r="H2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" s="1" t="n">
+        <v>46009.4426041667</v>
+      </c>
+      <c r="B2536" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C2536" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>0.0397999994456768</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H2536" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -70007,7 +70007,7 @@
     </row>
     <row r="2536">
       <c r="A2536" s="1" t="n">
-        <v>46009.4426041667</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2536" t="n">
         <v>45000</v>
@@ -70028,6 +70028,32 @@
         <v>1207</v>
       </c>
       <c r="H2536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" s="1" t="n">
+        <v>46010.6911342593</v>
+      </c>
+      <c r="B2537" t="n">
+        <v>210023</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>0.0417999997735023</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H2537" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -70033,7 +70033,7 @@
     </row>
     <row r="2537">
       <c r="A2537" s="1" t="n">
-        <v>46010.6911342593</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B2537" t="n">
         <v>210023</v>
@@ -70054,6 +70054,32 @@
         <v>1123</v>
       </c>
       <c r="H2537" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" s="1" t="n">
+        <v>46013.6100694444</v>
+      </c>
+      <c r="B2538" t="n">
+        <v>132274</v>
+      </c>
+      <c r="C2538" t="n">
+        <v>0.0406000018119812</v>
+      </c>
+      <c r="D2538" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="E2538" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="F2538" t="n">
+        <v>0.0403999984264374</v>
+      </c>
+      <c r="G2538" t="s">
+        <v>1244</v>
+      </c>
+      <c r="H2538" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -70059,7 +70059,7 @@
     </row>
     <row r="2538">
       <c r="A2538" s="1" t="n">
-        <v>46013.6100694444</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B2538" t="n">
         <v>132274</v>
@@ -70080,6 +70080,32 @@
         <v>1244</v>
       </c>
       <c r="H2538" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" s="1" t="n">
+        <v>46014.6911689815</v>
+      </c>
+      <c r="B2539" t="n">
+        <v>177791</v>
+      </c>
+      <c r="C2539" t="n">
+        <v>0.0408000014722347</v>
+      </c>
+      <c r="D2539" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="E2539" t="n">
+        <v>0.0399999991059303</v>
+      </c>
+      <c r="F2539" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="G2539" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H2539" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -70085,7 +70085,7 @@
     </row>
     <row r="2539">
       <c r="A2539" s="1" t="n">
-        <v>46014.6911689815</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2539" t="n">
         <v>177791</v>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -70109,6 +70109,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2540">
+      <c r="A2540" s="1" t="n">
+        <v>46020.3333333333</v>
+      </c>
+      <c r="B2540" t="n">
+        <v>47072</v>
+      </c>
+      <c r="C2540" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="D2540" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="E2540" t="n">
+        <v>0.0394000001251698</v>
+      </c>
+      <c r="F2540" t="n">
+        <v>0.0390000008046627</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NTW.MI.xlsx
+++ b/data/NTW.MI.xlsx
@@ -70135,6 +70135,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2541">
+      <c r="A2541" s="1" t="n">
+        <v>46021.3333333333</v>
+      </c>
+      <c r="B2541" t="n">
+        <v>284227</v>
+      </c>
+      <c r="C2541" t="n">
+        <v>0.0403999984264374</v>
+      </c>
+      <c r="D2541" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="E2541" t="n">
+        <v>0.0379999987781048</v>
+      </c>
+      <c r="F2541" t="n">
+        <v>0.0403999984264374</v>
+      </c>
+      <c r="G2541" t="s">
+        <v>1244</v>
+      </c>
+      <c r="H2541" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
